--- a/data/trans_orig/Q24A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fuman al día</t>
+          <t>Número medio de cigarrillos que fuman al día (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,86; 20,18</t>
+          <t>17,93; 20,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,97</t>
+          <t>17,37; 20,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,16; 17,81</t>
+          <t>15,14; 17,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,22; 18,22</t>
+          <t>15,34; 18,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,01; 14,63</t>
+          <t>11,89; 14,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,16; 14,73</t>
+          <t>12,15; 14,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,85</t>
+          <t>10,25; 13,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 12,05</t>
+          <t>9,88; 12,06</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,29; 18,11</t>
+          <t>16,22; 18,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,55; 17,52</t>
+          <t>15,51; 17,53</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,5; 15,53</t>
+          <t>13,53; 15,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,66; 15,71</t>
+          <t>13,52; 15,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,81; 16,98</t>
+          <t>15,77; 16,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,69; 15,99</t>
+          <t>14,72; 15,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 14,66</t>
+          <t>13,41; 14,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,15; 13,87</t>
+          <t>12,3; 13,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,82; 13,21</t>
+          <t>11,87; 13,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,19; 13,47</t>
+          <t>12,17; 13,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,57; 11,73</t>
+          <t>10,55; 11,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 10,3</t>
+          <t>9,25; 10,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 15,27</t>
+          <t>14,35; 15,26</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,78; 14,69</t>
+          <t>13,8; 14,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,31; 13,15</t>
+          <t>12,3; 13,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,11</t>
+          <t>11,08; 12,1</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 15,69</t>
+          <t>13,23; 15,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,51; 16,8</t>
+          <t>13,48; 16,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 13,12</t>
+          <t>10,15; 13,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,93; 15,44</t>
+          <t>11,0; 15,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,97; 14,49</t>
+          <t>10,96; 14,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 12,19</t>
+          <t>9,62; 12,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,53; 10,78</t>
+          <t>8,58; 10,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,02; 8,97</t>
+          <t>7,0; 9,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,63; 14,68</t>
+          <t>12,65; 14,62</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,91; 14,22</t>
+          <t>11,92; 14,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 11,52</t>
+          <t>9,68; 11,67</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,95</t>
+          <t>9,22; 11,75</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,34; 17,36</t>
+          <t>16,3; 17,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,56; 16,67</t>
+          <t>15,55; 16,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,59; 14,7</t>
+          <t>13,7; 14,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 14,37</t>
+          <t>12,92; 14,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 13,19</t>
+          <t>12,1; 13,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,16</t>
+          <t>12,06; 13,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,52; 11,51</t>
+          <t>10,49; 11,47</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 10,01</t>
+          <t>9,17; 10,0</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,87; 15,66</t>
+          <t>14,82; 15,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,22; 15,01</t>
+          <t>14,21; 14,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,36; 13,13</t>
+          <t>12,42; 13,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 12,29</t>
+          <t>11,44; 12,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,74</t>
+          <t>16,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>10,88</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,62</t>
+          <t>14,53</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>17,93; 20,28</t>
+          <t>17,87; 20,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,37; 20,08</t>
+          <t>17,32; 20,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 17,75</t>
+          <t>15,03; 17,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,34; 18,24</t>
+          <t>15,25; 18,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,89; 14,6</t>
+          <t>12,05; 14,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,15; 14,45</t>
+          <t>12,23; 14,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 13,07</t>
+          <t>10,28; 12,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 12,06</t>
+          <t>9,83; 12,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,22; 18,03</t>
+          <t>16,27; 18,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,53</t>
+          <t>15,56; 17,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13,53; 15,58</t>
+          <t>13,61; 15,58</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,78</t>
+          <t>13,5; 15,55</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13,06</t>
+          <t>13,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,72</t>
+          <t>9,79</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,58</t>
+          <t>11,73</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>15,77; 16,97</t>
+          <t>15,75; 17,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,72; 15,9</t>
+          <t>14,69; 15,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 14,6</t>
+          <t>13,44; 14,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 13,8</t>
+          <t>12,5; 14,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,87; 13,21</t>
+          <t>11,83; 13,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 13,42</t>
+          <t>12,21; 13,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,55; 11,67</t>
+          <t>10,54; 11,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 10,24</t>
+          <t>9,27; 10,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,35; 15,26</t>
+          <t>14,35; 15,22</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,8; 14,7</t>
+          <t>13,81; 14,65</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 13,1</t>
+          <t>12,31; 13,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,1</t>
+          <t>11,25; 12,27</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,93</t>
+          <t>7,94</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>10,19</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 15,61</t>
+          <t>13,18; 15,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,48; 16,71</t>
+          <t>13,29; 16,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 13,16</t>
+          <t>10,14; 13,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 15,69</t>
+          <t>10,93; 15,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 14,13</t>
+          <t>10,98; 14,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 12,46</t>
+          <t>9,6; 12,41</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,58; 10,76</t>
+          <t>8,54; 10,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,0; 9,0</t>
+          <t>6,95; 8,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12,65; 14,62</t>
+          <t>12,65; 14,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,92; 14,19</t>
+          <t>11,97; 14,07</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 11,67</t>
+          <t>9,77; 11,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,75</t>
+          <t>9,08; 11,71</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,64</t>
+          <t>13,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,84</t>
+          <t>11,93</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 17,36</t>
+          <t>16,36; 17,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 16,65</t>
+          <t>15,47; 16,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,7; 14,71</t>
+          <t>13,7; 14,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,92; 14,32</t>
+          <t>13,14; 14,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,1; 13,22</t>
+          <t>12,08; 13,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,1</t>
+          <t>12,04; 13,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 11,47</t>
+          <t>10,47; 11,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,17; 10,0</t>
+          <t>9,17; 10,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 15,64</t>
+          <t>14,88; 15,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 14,98</t>
+          <t>14,19; 15,01</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,42; 13,14</t>
+          <t>12,41; 13,13</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,44; 12,29</t>
+          <t>11,48; 12,35</t>
         </is>
       </c>
     </row>
